--- a/DesignData/WeaponConfig.xlsx
+++ b/DesignData/WeaponConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20415" windowHeight="12705"/>
+    <workbookView windowWidth="24885" windowHeight="12705"/>
   </bookViews>
   <sheets>
     <sheet name="WeaponConfig" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="30">
   <si>
     <t>WeaponType</t>
   </si>
@@ -57,6 +57,12 @@
   </si>
   <si>
     <t>Category</t>
+  </si>
+  <si>
+    <t>SpreadAngle</t>
+  </si>
+  <si>
+    <t>Penetration</t>
   </si>
   <si>
     <t>enum:WeaponTypeEnum</t>
@@ -581,155 +587,156 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1263,21 +1270,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="2" max="2" width="15.75" customWidth="1"/>
-    <col min="3" max="3" width="13.875" customWidth="1"/>
-    <col min="4" max="4" width="13.75" customWidth="1"/>
-    <col min="5" max="5" width="16.25" customWidth="1"/>
-    <col min="6" max="6" width="14.75" customWidth="1"/>
-    <col min="7" max="7" width="13.5" customWidth="1"/>
-    <col min="8" max="8" width="10.25" customWidth="1"/>
-    <col min="9" max="9" width="21.375" customWidth="1"/>
+    <col min="1" max="1" width="23" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.75" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="21.375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1308,45 +1315,57 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" t="s">
-        <v>11</v>
+      <c r="K2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3">
         <v>5</v>
@@ -1370,15 +1389,21 @@
         <v>0</v>
       </c>
       <c r="J3" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C4">
         <v>10</v>
@@ -1399,18 +1424,24 @@
         <v>840</v>
       </c>
       <c r="I4">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J4" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="K4">
+        <v>15</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1434,15 +1465,21 @@
         <v>0</v>
       </c>
       <c r="J5" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="K5">
+        <v>30</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1466,15 +1503,21 @@
         <v>0.2</v>
       </c>
       <c r="J6" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C7">
         <v>8</v>
@@ -1498,15 +1541,21 @@
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1530,7 +1579,13 @@
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="K8">
+        <v>5</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/DesignData/WeaponConfig.xlsx
+++ b/DesignData/WeaponConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="40">
   <si>
     <t>WeaponType</t>
   </si>
@@ -35,6 +35,9 @@
     <t>DisplayName</t>
   </si>
   <si>
+    <t>Description</t>
+  </si>
+  <si>
     <t>AmmoMul</t>
   </si>
   <si>
@@ -83,6 +86,9 @@
     <t>突击步枪</t>
   </si>
   <si>
+    <t>标准制式突击步枪，性能均衡，适用各种作战环境</t>
+  </si>
+  <si>
     <t>Handheld</t>
   </si>
   <si>
@@ -92,24 +98,36 @@
     <t>机枪</t>
   </si>
   <si>
+    <t>高射速压制武器，持续火力强劲，但精准度低</t>
+  </si>
+  <si>
     <t>SG</t>
   </si>
   <si>
     <t>霰弹枪</t>
   </si>
   <si>
+    <t>近距离大范围攻击，散射角度大</t>
+  </si>
+  <si>
     <t>MRL</t>
   </si>
   <si>
     <t>火箭发射器</t>
   </si>
   <si>
+    <t>重型反装甲武器，发射高爆火箭弹，威力巨大</t>
+  </si>
+  <si>
     <t>VML</t>
   </si>
   <si>
     <t>垂直导弹</t>
   </si>
   <si>
+    <t>垂直发射导弹系统，锁定当前瞄准的目标</t>
+  </si>
+  <si>
     <t>Hanger</t>
   </si>
   <si>
@@ -117,6 +135,18 @@
   </si>
   <si>
     <t>自动炮台</t>
+  </si>
+  <si>
+    <t>固定式自动炮台，提供持续火力支援</t>
+  </si>
+  <si>
+    <t>HSA</t>
+  </si>
+  <si>
+    <t>半自动加农炮</t>
+  </si>
+  <si>
+    <t>高精度高伤害的远程打击武器，可穿透多个目标</t>
   </si>
 </sst>
 </file>
@@ -1270,12 +1300,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="23" style="1" customWidth="1"/>
     <col min="2" max="2" width="15.75" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="50.75" style="1" customWidth="1"/>
     <col min="4" max="4" width="13.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.75" style="1" customWidth="1"/>
@@ -1284,7 +1314,7 @@
     <col min="9" max="9" width="21.375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1321,271 +1351,336 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
         <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I2" t="s">
         <v>15</v>
       </c>
       <c r="J2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>30</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>20</v>
+      </c>
+      <c r="H3">
+        <v>25</v>
+      </c>
+      <c r="I3">
+        <v>600</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3">
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
+      </c>
+      <c r="E4">
+        <v>60</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>25</v>
+      </c>
+      <c r="H4">
+        <v>10</v>
+      </c>
+      <c r="I4">
+        <v>840</v>
+      </c>
+      <c r="J4">
+        <v>0.1</v>
+      </c>
+      <c r="K4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L4">
         <v>15</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M4">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>30</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>20</v>
+      </c>
+      <c r="H5">
         <v>15</v>
       </c>
+      <c r="I5">
+        <v>180</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L5">
+        <v>30</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:12">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3">
-        <v>5</v>
-      </c>
-      <c r="D3">
+    <row r="6" spans="1:13">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
         <v>30</v>
       </c>
-      <c r="E3">
+      <c r="F6">
         <v>2</v>
       </c>
-      <c r="F3">
+      <c r="G6">
         <v>20</v>
       </c>
-      <c r="G3">
+      <c r="H6">
+        <v>15</v>
+      </c>
+      <c r="I6">
+        <v>120</v>
+      </c>
+      <c r="J6">
+        <v>0.2</v>
+      </c>
+      <c r="K6" t="s">
+        <v>20</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7">
+        <v>8</v>
+      </c>
+      <c r="E7">
+        <v>6</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>15</v>
+      </c>
+      <c r="H7">
         <v>25</v>
       </c>
-      <c r="H3">
-        <v>600</v>
-      </c>
-      <c r="I3">
+      <c r="I7">
+        <v>30</v>
+      </c>
+      <c r="J7">
         <v>0</v>
       </c>
-      <c r="J3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="L3">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4">
-        <v>10</v>
-      </c>
-      <c r="D4">
-        <v>60</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>25</v>
-      </c>
-      <c r="G4">
-        <v>10</v>
-      </c>
-      <c r="H4">
-        <v>840</v>
-      </c>
-      <c r="I4">
-        <v>0.1</v>
-      </c>
-      <c r="J4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K4">
-        <v>15</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>30</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>20</v>
-      </c>
-      <c r="G5">
-        <v>15</v>
-      </c>
-      <c r="H5">
-        <v>180</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K5">
-        <v>30</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6">
-        <v>30</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>20</v>
-      </c>
-      <c r="G6">
-        <v>15</v>
-      </c>
-      <c r="H6">
-        <v>120</v>
-      </c>
-      <c r="I6">
-        <v>0.2</v>
-      </c>
-      <c r="J6" t="s">
-        <v>18</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7">
-        <v>8</v>
-      </c>
-      <c r="D7">
-        <v>6</v>
-      </c>
-      <c r="E7">
-        <v>3</v>
-      </c>
-      <c r="F7">
-        <v>15</v>
-      </c>
-      <c r="G7">
-        <v>25</v>
-      </c>
-      <c r="H7">
-        <v>30</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
+      <c r="K7" t="s">
+        <v>33</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8">
+        <v>35</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8">
         <v>4</v>
       </c>
-      <c r="D8">
+      <c r="E8">
+        <v>100</v>
+      </c>
+      <c r="F8">
+        <v>4</v>
+      </c>
+      <c r="G8">
+        <v>30</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>640</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8" t="s">
+        <v>33</v>
+      </c>
+      <c r="L8">
+        <v>5</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9">
+        <v>5</v>
+      </c>
+      <c r="F9">
+        <v>3</v>
+      </c>
+      <c r="G9">
+        <v>50</v>
+      </c>
+      <c r="H9">
         <v>40</v>
       </c>
-      <c r="E8">
-        <v>4</v>
-      </c>
-      <c r="F8">
-        <v>30</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-      <c r="H8">
-        <v>300</v>
-      </c>
-      <c r="I8">
+      <c r="I9">
+        <v>120</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L9">
         <v>0</v>
       </c>
-      <c r="J8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K8">
-        <v>5</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
+      <c r="M9">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/DesignData/WeaponConfig.xlsx
+++ b/DesignData/WeaponConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="37">
   <si>
     <t>WeaponType</t>
   </si>
@@ -110,15 +110,6 @@
     <t>近距离大范围攻击，散射角度大</t>
   </si>
   <si>
-    <t>MRL</t>
-  </si>
-  <si>
-    <t>火箭发射器</t>
-  </si>
-  <si>
-    <t>重型反装甲武器，发射高爆火箭弹，威力巨大</t>
-  </si>
-  <si>
     <t>VML</t>
   </si>
   <si>
@@ -146,7 +137,7 @@
     <t>半自动加农炮</t>
   </si>
   <si>
-    <t>高精度高伤害的远程打击武器，可穿透多个目标</t>
+    <t>半自动加农炮，高精度远程打击武器</t>
   </si>
 </sst>
 </file>
@@ -1300,8 +1291,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="23" style="1" customWidth="1"/>
     <col min="2" max="2" width="15.75" style="1" customWidth="1"/>
@@ -1310,8 +1301,10 @@
     <col min="5" max="5" width="16.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.75" style="1" customWidth="1"/>
     <col min="7" max="7" width="13.5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="21.75" style="1" customWidth="1"/>
     <col min="9" max="9" width="21.375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.875" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -1410,7 +1403,7 @@
         <v>5</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -1422,7 +1415,7 @@
         <v>25</v>
       </c>
       <c r="I3">
-        <v>600</v>
+        <v>640</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1475,7 +1468,7 @@
         <v>15</v>
       </c>
       <c r="M4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1530,31 +1523,31 @@
         <v>29</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>15</v>
+      </c>
+      <c r="H6">
+        <v>25</v>
+      </c>
+      <c r="I6">
         <v>30</v>
       </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6">
-        <v>20</v>
-      </c>
-      <c r="H6">
-        <v>15</v>
-      </c>
-      <c r="I6">
-        <v>120</v>
-      </c>
       <c r="J6">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -1562,40 +1555,40 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7">
+        <v>4</v>
+      </c>
+      <c r="E7">
+        <v>100</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7">
         <v>30</v>
       </c>
-      <c r="B7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7">
-        <v>8</v>
-      </c>
-      <c r="E7">
-        <v>6</v>
-      </c>
-      <c r="F7">
-        <v>3</v>
-      </c>
-      <c r="G7">
-        <v>15</v>
-      </c>
       <c r="H7">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="I7">
-        <v>30</v>
+        <v>600</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -1615,71 +1608,30 @@
         <v>4</v>
       </c>
       <c r="E8">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H8">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="I8">
-        <v>640</v>
+        <v>120</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="L8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9">
-        <v>4</v>
-      </c>
-      <c r="E9">
-        <v>5</v>
-      </c>
-      <c r="F9">
-        <v>3</v>
-      </c>
-      <c r="G9">
-        <v>50</v>
-      </c>
-      <c r="H9">
-        <v>40</v>
-      </c>
-      <c r="I9">
-        <v>120</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
         <v>3</v>
       </c>
     </row>
